--- a/data_generation/06_soil_sorption/captan_soil_sorption.xlsx
+++ b/data_generation/06_soil_sorption/captan_soil_sorption.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\soil_sorption\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\06_soil_sorption\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F4B647-48E8-4835-B455-44B93A52ABD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFCAE6E-BC8A-48EE-B6E3-2902AD0BA7AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1430" yWindow="1540" windowWidth="32800" windowHeight="15410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,36 +33,6 @@
     <t>soil_name</t>
   </si>
   <si>
-    <t>soil_ph</t>
-  </si>
-  <si>
-    <t>p_clay</t>
-  </si>
-  <si>
-    <t>p_sand</t>
-  </si>
-  <si>
-    <t>p_silt</t>
-  </si>
-  <si>
-    <t>p_om</t>
-  </si>
-  <si>
-    <t>p_oc</t>
-  </si>
-  <si>
-    <t>kd</t>
-  </si>
-  <si>
-    <t>koc</t>
-  </si>
-  <si>
-    <t>kf</t>
-  </si>
-  <si>
-    <t>kfoc</t>
-  </si>
-  <si>
     <t>n</t>
   </si>
   <si>
@@ -93,22 +63,52 @@
     <t>j.efsa.2020.6230_LoEP</t>
   </si>
   <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>recorded</t>
+  </si>
+  <si>
+    <t>checked</t>
+  </si>
+  <si>
+    <t>rajo</t>
+  </si>
+  <si>
+    <t>soil_pH</t>
+  </si>
+  <si>
+    <t>pH_medium</t>
+  </si>
+  <si>
+    <t>f_clay</t>
+  </si>
+  <si>
+    <t>f_sand</t>
+  </si>
+  <si>
+    <t>f_silt</t>
+  </si>
+  <si>
+    <t>f_om</t>
+  </si>
+  <si>
+    <t>f_oc</t>
+  </si>
+  <si>
+    <t>Kd</t>
+  </si>
+  <si>
+    <t>Koc</t>
+  </si>
+  <si>
+    <t>Kf</t>
+  </si>
+  <si>
+    <t>Kfoc</t>
+  </si>
+  <si>
     <t>substance</t>
-  </si>
-  <si>
-    <t>note</t>
-  </si>
-  <si>
-    <t>recorded</t>
-  </si>
-  <si>
-    <t>checked</t>
-  </si>
-  <si>
-    <t>rajo</t>
-  </si>
-  <si>
-    <t>ph_medium</t>
   </si>
 </sst>
 </file>
@@ -496,17 +496,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="23.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="16" max="16" width="45.140625" customWidth="1"/>
+    <col min="1" max="2" width="23.26953125" customWidth="1"/>
+    <col min="3" max="3" width="19.26953125" customWidth="1"/>
+    <col min="5" max="5" width="12.7265625" customWidth="1"/>
+    <col min="16" max="16" width="45.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -515,87 +515,87 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="T1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>8</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>18</v>
       </c>
       <c r="L2">
         <v>76.8</v>
       </c>
       <c r="P2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="Q2">
         <v>44</v>
       </c>
       <c r="R2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="S2" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="T2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="U2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
